--- a/projetos/OBRA_TMULT/05_SUPRIMENTOS_E_FINANCEIRO/FLUXO_DE_CAIXA_TMULT.xlsx
+++ b/projetos/OBRA_TMULT/05_SUPRIMENTOS_E_FINANCEIRO/FLUXO_DE_CAIXA_TMULT.xlsx
@@ -927,7 +927,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Empreendimento: TMULT — Terminal Multiuso (Porto do Açu) | Prazo: 6 Meses (180 Dias) | Baseline 01</t>
+          <t>Empreendimento: TMULT — Terminal Multiuso (Porto do Açu) — Edifício Administrativo | Prazo: 6 Meses (180 Dias) | Baseline 01</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="E9" s="7" t="n">
-        <v>98592.17999999999</v>
+        <v>98649.3</v>
       </c>
     </row>
     <row r="10">
@@ -985,7 +985,7 @@
         </is>
       </c>
       <c r="E10" s="9" t="n">
-        <v>103951.57</v>
+        <v>103894.45</v>
       </c>
     </row>
     <row r="11">
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="E11" s="10" t="n">
-        <v>0.06259268484830954</v>
+        <v>0.06255829100357459</v>
       </c>
     </row>
     <row r="12">
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>180593.13</v>
+        <v>180621.7</v>
       </c>
     </row>
     <row r="14">
@@ -1079,13 +1079,13 @@
         <v>0</v>
       </c>
       <c r="D18" s="17" t="n">
-        <v>105458.24</v>
+        <v>105467.76</v>
       </c>
       <c r="E18" s="17" t="n">
-        <v>-105458.24</v>
+        <v>-105467.76</v>
       </c>
       <c r="F18" s="18" t="n">
-        <v>-105458.24</v>
+        <v>-105467.76</v>
       </c>
     </row>
     <row r="19">
@@ -1098,13 +1098,13 @@
         <v>155269.92</v>
       </c>
       <c r="D19" s="20" t="n">
-        <v>202180.93</v>
+        <v>202190.46</v>
       </c>
       <c r="E19" s="20" t="n">
-        <v>-46911.01</v>
+        <v>-46920.54</v>
       </c>
       <c r="F19" s="21" t="n">
-        <v>-152369.25</v>
+        <v>-152388.3</v>
       </c>
     </row>
     <row r="20">
@@ -1117,13 +1117,13 @@
         <v>264001.06</v>
       </c>
       <c r="D20" s="17" t="n">
-        <v>292224.94</v>
+        <v>292234.46</v>
       </c>
       <c r="E20" s="17" t="n">
-        <v>-28223.88</v>
+        <v>-28233.4</v>
       </c>
       <c r="F20" s="18" t="n">
-        <v>-180593.13</v>
+        <v>-180621.7</v>
       </c>
     </row>
     <row r="21">
@@ -1136,13 +1136,13 @@
         <v>348054.46</v>
       </c>
       <c r="D21" s="20" t="n">
-        <v>290508</v>
+        <v>290517.52</v>
       </c>
       <c r="E21" s="20" t="n">
-        <v>57546.46</v>
+        <v>57536.94</v>
       </c>
       <c r="F21" s="21" t="n">
-        <v>-123046.67</v>
+        <v>-123084.76</v>
       </c>
     </row>
     <row r="22">
@@ -1155,13 +1155,13 @@
         <v>233397.32</v>
       </c>
       <c r="D22" s="17" t="n">
-        <v>259904.6</v>
+        <v>259914.12</v>
       </c>
       <c r="E22" s="17" t="n">
-        <v>-26507.28</v>
+        <v>-26516.8</v>
       </c>
       <c r="F22" s="18" t="n">
-        <v>-149553.95</v>
+        <v>-149601.56</v>
       </c>
     </row>
     <row r="23">
@@ -1174,13 +1174,13 @@
         <v>304396.06</v>
       </c>
       <c r="D23" s="20" t="n">
-        <v>287948.47</v>
+        <v>287957.98</v>
       </c>
       <c r="E23" s="20" t="n">
-        <v>16447.59</v>
+        <v>16438.08</v>
       </c>
       <c r="F23" s="21" t="n">
-        <v>-133106.36</v>
+        <v>-133163.48</v>
       </c>
     </row>
     <row r="24">
@@ -1199,7 +1199,7 @@
         <v>237057.93</v>
       </c>
       <c r="F24" s="22" t="n">
-        <v>103951.57</v>
+        <v>103894.45</v>
       </c>
     </row>
     <row r="25">
@@ -1212,13 +1212,13 @@
         <v>1660762.28</v>
       </c>
       <c r="D25" s="24" t="n">
-        <v>1556810.71</v>
+        <v>1556867.83</v>
       </c>
       <c r="E25" s="24" t="n">
-        <v>103951.57</v>
+        <v>103894.45</v>
       </c>
       <c r="F25" s="24" t="n">
-        <v>103951.57</v>
+        <v>103894.45</v>
       </c>
     </row>
   </sheetData>
@@ -1253,14 +1253,14 @@
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -1711,7 +1711,7 @@
         <v>0</v>
       </c>
       <c r="D15" s="17" t="n">
-        <v>35046.06</v>
+        <v>35046.07</v>
       </c>
       <c r="E15" s="17" t="n">
         <v>81815.99000000001</v>
@@ -1723,7 +1723,7 @@
         <v>68652.02</v>
       </c>
       <c r="H15" s="17" t="n">
-        <v>100237.01</v>
+        <v>100237</v>
       </c>
       <c r="I15" s="17" t="n">
         <v>89397.44</v>
@@ -1852,28 +1852,28 @@
         </is>
       </c>
       <c r="C19" s="17" t="n">
-        <v>16432.03</v>
+        <v>16441.55</v>
       </c>
       <c r="D19" s="17" t="n">
-        <v>16432.03</v>
+        <v>16441.55</v>
       </c>
       <c r="E19" s="17" t="n">
-        <v>16432.03</v>
+        <v>16441.55</v>
       </c>
       <c r="F19" s="17" t="n">
-        <v>16432.03</v>
+        <v>16441.55</v>
       </c>
       <c r="G19" s="17" t="n">
-        <v>16432.03</v>
+        <v>16441.55</v>
       </c>
       <c r="H19" s="17" t="n">
-        <v>16432.03</v>
+        <v>16441.55</v>
       </c>
       <c r="I19" s="17" t="n">
         <v>0</v>
       </c>
       <c r="J19" s="29" t="n">
-        <v>98592.17999999999</v>
+        <v>98649.3</v>
       </c>
     </row>
     <row r="20">
@@ -1888,28 +1888,28 @@
         </is>
       </c>
       <c r="C20" s="27" t="n">
-        <v>105458.24</v>
+        <v>105467.76</v>
       </c>
       <c r="D20" s="27" t="n">
-        <v>202180.93</v>
+        <v>202190.46</v>
       </c>
       <c r="E20" s="27" t="n">
-        <v>292224.94</v>
+        <v>292234.46</v>
       </c>
       <c r="F20" s="27" t="n">
-        <v>290508</v>
+        <v>290517.52</v>
       </c>
       <c r="G20" s="27" t="n">
-        <v>259904.6</v>
+        <v>259914.12</v>
       </c>
       <c r="H20" s="27" t="n">
-        <v>287948.47</v>
+        <v>287957.98</v>
       </c>
       <c r="I20" s="27" t="n">
         <v>118585.53</v>
       </c>
       <c r="J20" s="27" t="n">
-        <v>1556810.71</v>
+        <v>1556867.83</v>
       </c>
     </row>
     <row r="21">
@@ -1931,28 +1931,28 @@
         </is>
       </c>
       <c r="C22" s="27" t="n">
-        <v>-105458.24</v>
+        <v>-105467.76</v>
       </c>
       <c r="D22" s="27" t="n">
-        <v>-46911.01</v>
+        <v>-46920.54</v>
       </c>
       <c r="E22" s="27" t="n">
-        <v>-28223.88</v>
+        <v>-28233.4</v>
       </c>
       <c r="F22" s="27" t="n">
-        <v>57546.46</v>
+        <v>57536.94</v>
       </c>
       <c r="G22" s="27" t="n">
-        <v>-26507.28</v>
+        <v>-26516.8</v>
       </c>
       <c r="H22" s="27" t="n">
-        <v>16447.59</v>
+        <v>16438.08</v>
       </c>
       <c r="I22" s="27" t="n">
         <v>237057.93</v>
       </c>
       <c r="J22" s="27" t="n">
-        <v>103951.57</v>
+        <v>103894.45</v>
       </c>
     </row>
     <row r="23">
@@ -1967,28 +1967,28 @@
         </is>
       </c>
       <c r="C23" s="35" t="n">
-        <v>-105458.24</v>
+        <v>-105467.76</v>
       </c>
       <c r="D23" s="35" t="n">
-        <v>-152369.25</v>
+        <v>-152388.3</v>
       </c>
       <c r="E23" s="35" t="n">
-        <v>-180593.13</v>
+        <v>-180621.7</v>
       </c>
       <c r="F23" s="35" t="n">
-        <v>-123046.67</v>
+        <v>-123084.76</v>
       </c>
       <c r="G23" s="35" t="n">
-        <v>-149553.95</v>
+        <v>-149601.56</v>
       </c>
       <c r="H23" s="35" t="n">
-        <v>-133106.36</v>
+        <v>-133163.48</v>
       </c>
       <c r="I23" s="36" t="n">
-        <v>103951.57</v>
+        <v>103894.45</v>
       </c>
       <c r="J23" s="37" t="n">
-        <v>103951.57</v>
+        <v>103894.45</v>
       </c>
     </row>
   </sheetData>
@@ -2013,16 +2013,16 @@
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
     <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -2106,25 +2106,25 @@
         </is>
       </c>
       <c r="C3" s="18" t="n">
-        <v>-105458.24</v>
+        <v>-105467.76</v>
       </c>
       <c r="D3" s="18" t="n">
-        <v>-152369.25</v>
+        <v>-152388.3</v>
       </c>
       <c r="E3" s="18" t="n">
-        <v>-180593.13</v>
+        <v>-180621.7</v>
       </c>
       <c r="F3" s="18" t="n">
-        <v>-123046.67</v>
+        <v>-123084.76</v>
       </c>
       <c r="G3" s="18" t="n">
-        <v>-149553.95</v>
+        <v>-149601.56</v>
       </c>
       <c r="H3" s="18" t="n">
-        <v>-133106.36</v>
+        <v>-133163.48</v>
       </c>
       <c r="I3" s="22" t="n">
-        <v>103951.57</v>
+        <v>103894.45</v>
       </c>
       <c r="J3" s="39" t="inlineStr">
         <is>
@@ -2132,10 +2132,10 @@
         </is>
       </c>
       <c r="K3" s="18" t="n">
-        <v>-180593.13</v>
+        <v>-180621.7</v>
       </c>
       <c r="L3" s="29" t="n">
-        <v>103951.57</v>
+        <v>103894.45</v>
       </c>
     </row>
     <row r="4">
@@ -2146,29 +2146,29 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>Adiantamento Contratual de 10% (R$ 166.076,23) amortizado em 4x nas medições</t>
+          <t>Adiantamento Contratual de 10% amortizado em 4x nas medições</t>
         </is>
       </c>
       <c r="C4" s="40" t="n">
-        <v>60617.99</v>
+        <v>60608.47</v>
       </c>
       <c r="D4" s="21" t="n">
-        <v>-27812.08</v>
+        <v>-27831.13</v>
       </c>
       <c r="E4" s="21" t="n">
-        <v>-97555.02</v>
+        <v>-97583.59</v>
       </c>
       <c r="F4" s="21" t="n">
-        <v>-81527.62</v>
+        <v>-81565.71000000001</v>
       </c>
       <c r="G4" s="21" t="n">
-        <v>-149553.96</v>
+        <v>-149601.57</v>
       </c>
       <c r="H4" s="21" t="n">
-        <v>-133106.37</v>
+        <v>-133163.49</v>
       </c>
       <c r="I4" s="40" t="n">
-        <v>103951.56</v>
+        <v>103894.44</v>
       </c>
       <c r="J4" s="41" t="inlineStr">
         <is>
@@ -2176,10 +2176,10 @@
         </is>
       </c>
       <c r="K4" s="21" t="n">
-        <v>-149553.96</v>
+        <v>-149601.57</v>
       </c>
       <c r="L4" s="27" t="n">
-        <v>103951.56</v>
+        <v>103894.44</v>
       </c>
     </row>
     <row r="5">
@@ -2194,39 +2194,39 @@
         </is>
       </c>
       <c r="C5" s="18" t="n">
-        <v>-105458.24</v>
+        <v>-105467.76</v>
       </c>
       <c r="D5" s="18" t="n">
-        <v>-307639.17</v>
+        <v>-307658.22</v>
       </c>
       <c r="E5" s="18" t="n">
-        <v>-444594.19</v>
+        <v>-444622.76</v>
       </c>
       <c r="F5" s="18" t="n">
-        <v>-471101.13</v>
+        <v>-471139.22</v>
       </c>
       <c r="G5" s="18" t="n">
-        <v>-382951.27</v>
+        <v>-382998.88</v>
       </c>
       <c r="H5" s="18" t="n">
-        <v>-437502.42</v>
+        <v>-437559.54</v>
       </c>
       <c r="I5" s="18" t="n">
-        <v>-251691.89</v>
+        <v>-251749.01</v>
       </c>
       <c r="J5" s="22" t="n">
-        <v>103951.57</v>
+        <v>103894.45</v>
       </c>
       <c r="K5" s="18" t="n">
-        <v>-471101.13</v>
+        <v>-471139.22</v>
       </c>
       <c r="L5" s="29" t="n">
-        <v>103951.57</v>
+        <v>103894.45</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A1:L1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
